--- a/test-data/excel/manual-test-cases.xlsx
+++ b/test-data/excel/manual-test-cases.xlsx
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Add a new employee (happy path)</t>
+          <t>Add a new employee and populate Personal Details (happy path)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Verify that a new employee can be created by supplying only the two mandatory name fields, and that the record appears correctly in the Employee List.</t>
+          <t>Verify that a new employee can be created by supplying the mandatory name fields, and that the additional Personal Details fields not exposed on the Add Employee form itself (Driver's License Number, License Expiry Date, Nationality, Marital Status, Date of Birth, Gender, and the separate Custom Fields section's Blood Type/Test_Field) are entered, saved, and read back exactly as entered.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1380,21 +1380,22 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>First Name: a unique generated value (e.g. "AutoQA_&lt;timestamp&gt;") | Last Name: "TestUser"</t>
+          <t>First Name/Last Name: a real-looking generated pair | Employee Id: a unique generated value | Driver's License Number: a random 8-digit value | License Expiry Date: a random future date | Nationality: "Indian" | Marital Status: "Single" or "Married" | Date of Birth: a random past date | Gender: "Male" or "Female" | Blood Type: a random valid type (e.g. "A+") | Test_Field: a unique generated value</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>1. Navigate to PIM &gt; Add Employee.
-2. Enter a unique First Name.
-3. Enter a Last Name.
-4. Note the system-generated Employee Id.
-5. Click Save.</t>
+2. Enter a unique First Name and Last Name.
+3. Note/override the system-generated Employee Id.
+4. Click Save.
+5. On the resulting Personal Details page, enter Driver's License Number and License Expiry Date, select Nationality and Marital Status, enter Date of Birth, and select Gender, then click the Personal Details Save button.
+6. Under the separate Custom Fields section, select Blood Type and enter Test_Field, then click its own Save button.</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>The employee is created without error, the app navigates to that employee's Personal Details page, and the new employee subsequently appears in the Employee List with the same name and Employee Id.</t>
+          <t>The employee is created without error, the app navigates to that employee's Personal Details page, and the new employee subsequently appears in the Employee List with the same name and Employee Id. After the two additional saves, every field entered (Driver's License Number, License Expiry Date, Nationality, Marital Status, Date of Birth, Gender, Blood Type, Test_Field) is shown exactly as entered - confirming the Personal Details form and the independent Custom Fields form (its own separate Save button, verified live) both persist correctly.</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
@@ -1718,7 +1719,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>Verify that selecting values in the Nationality and Marital Status dropdowns on an employee's Personal Details tab persists after saving.</t>
+          <t>Verify that selecting values in the Nationality and Marital Status dropdowns on an employee's Personal Details tab persists after saving. (Note: selecting and saving Nationality/Marital Status on a newly created employee, without an explicit reload, is also exercised by TC-PIM-006/TC-PIM-013's automated additional-details flow - this case specifically verifies persistence via a page reload on an existing record, which those automated cases don't perform.)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2700,12 +2701,12 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Data-driven employee creation</t>
+          <t>Data-driven employee creation with Personal Details</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>Verify that multiple employees can be created from an external Excel data source, each landing correctly in the Employee List.</t>
+          <t>Verify that multiple employees can be created from an external Excel data source, each landing correctly in the Employee List, and that each generated row also has its Date of Birth, Gender, and Blood Type entered on Personal Details and read back correctly (the remaining additional fields - Driver's License Number, License Expiry Date, Nationality, Marital Status, Test_Field - are filled and saved for every row too, but only independently re-verified once, in TC-PIM-006).</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -2715,19 +2716,20 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>test-data/excel driven rows, e.g.: (AutoQA_01, TestUser), (AutoQA_02, TestUser), (AutoQA_03, TestUser)</t>
+          <t>test-data/excel driven rows, e.g.: (Sachin, Tendulkar), (Virat, Kohli), (Rohit, Sharma) | per row: a random Date of Birth, Gender, and Blood Type</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
           <t>1. Load employee records from the Excel test-data file.
 2. For each row, navigate to Add Employee, enter the First/Last Name from that row, and Save.
-3. After all rows are processed, search the Employee List for each created name.</t>
+3. On the resulting Personal Details page, fill and save the additional fields (Driver's License Number, License Expiry Date, Nationality, Marital Status, Date of Birth, Gender) and the Custom Fields (Blood Type, Test_Field).
+4. After all rows are processed, confirm each row's Date of Birth, Gender, and Blood Type were saved correctly.</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Every employee row from the source Excel file results in a corresponding employee record that is found in the Employee List with matching First and Last Name.</t>
+          <t>Every employee row from the source Excel file results in a corresponding employee record with matching First and Last Name, and that record's Date of Birth, Gender, and Blood Type are shown exactly as entered on Personal Details.</t>
         </is>
       </c>
       <c r="J34" s="8" t="inlineStr">
